--- a/media/exports/reports/2026-03/calls.xlsx
+++ b/media/exports/reports/2026-03/calls.xlsx
@@ -690,7 +690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>February 763</t>
+          <t>February 678</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>405 calls to voicemail</t>
+          <t>444 calls to voicemail</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>299 answered calls</t>
+          <t>338 answered calls</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>774 calls for help came in during March. While the line was staffed, 81.0% were answered (target 90.0%); 52.3% of all calls came outside staffed hours and went to voicemail. The busiest time was 5 to 8pm (171 calls).</t>
+          <t>865 calls for help came in during March. While the line was staffed, 80.3% were answered (target 90.0%); 51.3% of all calls came outside staffed hours and went to voicemail. The busiest time was 5 to 8pm (181 calls).</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>171 calls came between 5 and 8pm, when no-one is on the line. 70 callers hung up waiting while the line was staffed.</t>
+          <t>181 calls came between 5 and 8pm, when no-one is on the line. 83 callers hung up waiting while the line was staffed.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1013,7 +1013,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>774</v>
+        <v>865</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>763</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>774</v>
+        <v>865</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>763</v>
+        <v>678</v>
       </c>
     </row>
     <row r="19">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>774</v>
+        <v>865</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>763</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31">
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>774</v>
+        <v>865</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>763</v>
+        <v>678</v>
       </c>
     </row>
     <row r="39">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B67" s="13" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B75" s="13" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86">
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="B93" s="13" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="B102" s="13" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
@@ -1851,7 +1851,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1899,7 +1899,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>659</v>
+        <v>685</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="F6" s="14">
         <f>IF(D6=0,"",E6/D6)</f>
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F7" s="14">
         <f>IF(D7=0,"",E7/D7)</f>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>284</v>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>324</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F9" s="14">
         <f>IF(D9=0,"",E9/D9)</f>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F10" s="14">
         <f>IF(D10=0,"",E10/D10)</f>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>725</v>
+        <v>685</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="F11" s="14">
         <f>IF(D11=0,"",E11/D11)</f>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="F12" s="14">
         <f>IF(D12=0,"",E12/D12)</f>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>754</v>
+        <v>724</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F13" s="14">
         <f>IF(D13=0,"",E13/D13)</f>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>783</v>
+        <v>820</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F14" s="14">
         <f>IF(D14=0,"",E14/D14)</f>
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>871</v>
+        <v>909</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="F15" s="14">
         <f>IF(D15=0,"",E15/D15)</f>
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>852</v>
+        <v>826</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="F16" s="14">
         <f>IF(D16=0,"",E16/D16)</f>
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F17" s="14">
         <f>IF(D17=0,"",E17/D17)</f>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F18" s="14">
         <f>IF(D18=0,"",E18/D18)</f>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>675</v>
+        <v>746</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="F19" s="14">
         <f>IF(D19=0,"",E19/D19)</f>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>725</v>
+        <v>776</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F20" s="14">
         <f>IF(D20=0,"",E20/D20)</f>
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>756</v>
+        <v>726</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="F21" s="14">
         <f>IF(D21=0,"",E21/D21)</f>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>763</v>
+        <v>678</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
       <c r="F22" s="14">
         <f>IF(D22=0,"",E22/D22)</f>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>774</v>
+        <v>865</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="F23" s="14">
         <f>IF(D23=0,"",E23/D23)</f>
@@ -2392,7 +2392,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-03/calls.xlsx
+++ b/media/exports/reports/2026-03/calls.xlsx
@@ -17,7 +17,7 @@
     <definedName name="Calls_outside_staffed_hours_March">'Report'!$B$10</definedName>
     <definedName name="Median_wait_when_answered_March">'Report'!$B$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$105</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$23</definedName>
   </definedNames>
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,8 +134,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,6 +147,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -690,7 +693,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -774,8 +777,8 @@
           <t>Median wait when answered, March</t>
         </is>
       </c>
-      <c r="B11" s="6">
-        <f>Workings!B42</f>
+      <c r="B11" s="8">
+        <f>Workings!B39</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -786,7 +789,7 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>When the calls come in, March 2026</t>
         </is>
@@ -811,12 +814,12 @@
           <t>Before 8:30am</t>
         </is>
       </c>
-      <c r="B15" s="9">
-        <f>Workings!B49</f>
+      <c r="B15" s="8">
+        <f>Workings!B47</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>Workings!B50</f>
+        <f>Workings!B48</f>
         <v/>
       </c>
     </row>
@@ -826,12 +829,12 @@
           <t>8:30 to 10am</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>Workings!B58</f>
+      <c r="B16" s="8">
+        <f>Workings!B56</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>Workings!B59</f>
+        <f>Workings!B57</f>
         <v/>
       </c>
     </row>
@@ -841,12 +844,12 @@
           <t>10am to noon</t>
         </is>
       </c>
-      <c r="B17" s="9">
-        <f>Workings!B67</f>
+      <c r="B17" s="8">
+        <f>Workings!B65</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>Workings!B68</f>
+        <f>Workings!B66</f>
         <v/>
       </c>
     </row>
@@ -856,12 +859,12 @@
           <t>Noon to 2pm</t>
         </is>
       </c>
-      <c r="B18" s="9">
-        <f>Workings!B76</f>
+      <c r="B18" s="8">
+        <f>Workings!B74</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>Workings!B77</f>
+        <f>Workings!B75</f>
         <v/>
       </c>
     </row>
@@ -871,12 +874,12 @@
           <t>2 to 5pm</t>
         </is>
       </c>
-      <c r="B19" s="9">
-        <f>Workings!B85</f>
+      <c r="B19" s="8">
+        <f>Workings!B83</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>Workings!B86</f>
+        <f>Workings!B84</f>
         <v/>
       </c>
     </row>
@@ -886,12 +889,12 @@
           <t>5 to 8pm</t>
         </is>
       </c>
-      <c r="B20" s="9">
-        <f>Workings!B94</f>
+      <c r="B20" s="8">
+        <f>Workings!B92</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>Workings!B95</f>
+        <f>Workings!B93</f>
         <v/>
       </c>
     </row>
@@ -901,12 +904,12 @@
           <t>After 8pm</t>
         </is>
       </c>
-      <c r="B21" s="9">
-        <f>Workings!B103</f>
+      <c r="B21" s="8">
+        <f>Workings!B101</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>Workings!B104</f>
+        <f>Workings!B102</f>
         <v/>
       </c>
     </row>
@@ -968,7 +971,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -987,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1013,7 +1016,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1315,14 +1318,14 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Calls for help, March and February</t>
+          <t>Median wait when answered, March and February</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Answered ÷ calls while the line was staffed</t>
+          <t>The middle wait when every answered call is lined up from shortest to longest</t>
         </is>
       </c>
     </row>
@@ -1342,516 +1345,480 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Answered calls (while staffed)</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>338</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Median wait (seconds, rounded half up)</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">March: 338 waits in order; the median is halfway between the 169th and 170th (76 and 78 seconds). Unanswered calls and calls outside staffed hours have no wait to count. </t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Calls before 8:30am, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Answered ÷ calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Calls</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n">
-        <v>865</v>
-      </c>
-      <c r="C38" s="13" t="n">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Calls while staffed</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n">
-        <v>421</v>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="B46" s="13" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
-        <v>338</v>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Answered while staffed</t>
-        </is>
-      </c>
-      <c r="B41" s="14">
-        <f>B40/B39</f>
-        <v/>
-      </c>
-      <c r="C41" s="14">
-        <f>C40/C39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Calls outside staffed hours</t>
-        </is>
-      </c>
-      <c r="B42" s="16">
-        <f>(B38-B39)/B38</f>
-        <v/>
-      </c>
-      <c r="C42" s="16">
-        <f>(C38-C39)/C38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>Calls before 8:30am, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="B47" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B48" s="16">
+        <f>B47/B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Calls 8:30 to 10am, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Calls</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="B55" s="13" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n">
+      <c r="B56" s="13" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B57" s="16">
+        <f>B56/B55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Calls 10am to noon, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Answered ÷ calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B66" s="16">
+        <f>B65/B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Calls noon to 2pm, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Answered ÷ calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr"/>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B75" s="16">
+        <f>B74/B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Calls 2 to 5pm, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Answered ÷ calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr"/>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B84" s="16">
+        <f>B83/B82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>Calls 5 to 8pm, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Answered ÷ calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr"/>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B50" s="16">
-        <f>B49/B48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="B93" s="16">
+        <f>B92/B91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Calls 8:30 to 10am, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>Calls after 8pm, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr"/>
-      <c r="B56" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr"/>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Calls</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="B100" s="13" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="B101" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B59" s="16">
-        <f>B58/B57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="B102" s="16">
+        <f>B101/B100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Calls 10am to noon, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Answered ÷ calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr"/>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Calls</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B68" s="16">
-        <f>B67/B66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>Calls noon to 2pm, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Answered ÷ calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr"/>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Calls</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Calls 2 to 5pm, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Answered ÷ calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr"/>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Calls</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="15" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B86" s="16">
-        <f>B85/B84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>Calls 5 to 8pm, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Answered ÷ calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr"/>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Calls</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B94" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B95" s="16">
-        <f>B94/B93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="12" t="inlineStr">
-        <is>
-          <t>Calls after 8pm, March 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Answered ÷ calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr"/>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Calls</t>
-        </is>
-      </c>
-      <c r="B102" s="13" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="B104" s="16">
-        <f>B103/B102</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Outside 8:30am to 5pm on working days the line goes to voicemail.</t>
-        </is>
-      </c>
-    </row>
+    <row r="104"/>
+    <row r="105"/>
     <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1859,8 +1826,8 @@
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="24" min="0" max="16383" man="1"/>
-    <brk id="53" min="0" max="16383" man="1"/>
-    <brk id="80" min="0" max="16383" man="1"/>
+    <brk id="51" min="0" max="16383" man="1"/>
+    <brk id="78" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1899,7 +1866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1904,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -1962,12 +1929,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -1987,12 +1954,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2012,12 +1979,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2037,12 +2004,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2062,12 +2029,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2087,12 +2054,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2112,12 +2079,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2137,12 +2104,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2162,12 +2129,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2187,12 +2154,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2212,12 +2179,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2237,12 +2204,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2262,12 +2229,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2287,12 +2254,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2312,12 +2279,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2337,12 +2304,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2362,12 +2329,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
@@ -2392,7 +2359,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-03/calls.xlsx
+++ b/media/exports/reports/2026-03/calls.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Calls_for_help_March">'Report'!$B$8</definedName>
-    <definedName name="Answered_while_staffed_March">'Report'!$B$9</definedName>
-    <definedName name="Calls_outside_staffed_hours_March">'Report'!$B$10</definedName>
-    <definedName name="Median_wait_when_answered_March">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$36</definedName>
+    <definedName name="Calls_for_help_March">'Report'!$B$9</definedName>
+    <definedName name="Answered_while_staffed_March">'Report'!$B$10</definedName>
+    <definedName name="Calls_outside_staffed_hours_March">'Report'!$B$11</definedName>
+    <definedName name="Median_wait_when_answered_March">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$23</definedName>
@@ -55,6 +55,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -75,11 +80,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -117,39 +117,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -293,12 +296,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$21</f>
+              <f>'Report'!$A$16:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$21</f>
+              <f>'Report'!$B$16:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -342,7 +345,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2610000"/>
@@ -667,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -693,7 +696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -701,219 +704,225 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 865 calls in March: 80.3% answered while staffed (target 90.0%); 51.3% came outside staffed hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every call to the help line: when it came in, whether someone answered, and how long the caller waited. The line is staffed 8:30am to 5pm on working days.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Calls for help, March</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B12</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 678</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Answered while staffed, March</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B22</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>target 90.0%</t>
+          <t>Calls for help, March</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>February 678</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Calls outside staffed hours, March</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>Workings!B32</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>444 calls to voicemail</t>
+          <t>Answered while staffed, March</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>Workings!B21</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>target 90.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Calls outside staffed hours, March</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>Workings!B32</f>
+        <v/>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>444 calls to voicemail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Median wait when answered, March</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B12" s="7">
         <f>Workings!B39</f>
         <v/>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>338 answered calls</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>When the calls come in, March 2026</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Calls</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Answered %</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Before 8:30am</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>Workings!B47</f>
-        <v/>
-      </c>
-      <c r="C15" s="6">
-        <f>Workings!B48</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8:30 to 10am</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Workings!B56</f>
-        <v/>
-      </c>
-      <c r="C16" s="6">
-        <f>Workings!B57</f>
+          <t>Before 8:30am</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>Workings!B46</f>
+        <v/>
+      </c>
+      <c r="C16" s="9">
+        <f>Workings!B48</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10am to noon</t>
-        </is>
-      </c>
-      <c r="B17" s="8">
-        <f>Workings!B65</f>
-        <v/>
-      </c>
-      <c r="C17" s="6">
-        <f>Workings!B66</f>
+          <t>8:30 to 10am</t>
+        </is>
+      </c>
+      <c r="B17" s="7">
+        <f>Workings!B55</f>
+        <v/>
+      </c>
+      <c r="C17" s="9">
+        <f>Workings!B57</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Noon to 2pm</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>Workings!B74</f>
-        <v/>
-      </c>
-      <c r="C18" s="6">
-        <f>Workings!B75</f>
+          <t>10am to noon</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>Workings!B64</f>
+        <v/>
+      </c>
+      <c r="C18" s="9">
+        <f>Workings!B66</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2 to 5pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B83</f>
-        <v/>
-      </c>
-      <c r="C19" s="6">
-        <f>Workings!B84</f>
+          <t>Noon to 2pm</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>Workings!B73</f>
+        <v/>
+      </c>
+      <c r="C19" s="9">
+        <f>Workings!B75</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5 to 8pm</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B92</f>
-        <v/>
-      </c>
-      <c r="C20" s="6">
-        <f>Workings!B93</f>
+          <t>2 to 5pm</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>Workings!B82</f>
+        <v/>
+      </c>
+      <c r="C20" s="9">
+        <f>Workings!B84</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>5 to 8pm</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>Workings!B91</f>
+        <v/>
+      </c>
+      <c r="C21" s="9">
+        <f>Workings!B93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>After 8pm</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B101</f>
-        <v/>
-      </c>
-      <c r="C21" s="6">
+      <c r="B22" s="7">
+        <f>Workings!B100</f>
+        <v/>
+      </c>
+      <c r="C22" s="9">
         <f>Workings!B102</f>
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
@@ -921,64 +930,66 @@
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Calls for help by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>865 calls for help came in during March. While the line was staffed, 80.3% were answered (target 90.0%); 51.3% of all calls came outside staffed hours and went to voicemail. The busiest time was 5 to 8pm (181 calls).</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>181 calls came between 5 and 8pm, when no-one is on the line. 83 callers hung up waiting while the line was staffed.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38"/>
+    <row r="39"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="13" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1016,33 +1027,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Calls for help, March and February</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls while the line was staffed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
@@ -1054,10 +1065,10 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>865</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>678</v>
       </c>
     </row>
@@ -1067,10 +1078,10 @@
           <t>Calls while staffed</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>421</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>341</v>
       </c>
     </row>
@@ -1080,10 +1091,10 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>275</v>
       </c>
     </row>
@@ -1093,26 +1104,26 @@
           <t>Answered while staffed</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <f>B10/B9</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="15">
         <f>C10/C9</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Calls outside staffed hours</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <f>(B8-B9)/B8</f>
         <v/>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>(C8-C9)/C8</f>
         <v/>
       </c>
@@ -1120,27 +1131,27 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Calls for help, March and February</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls while the line was staffed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
@@ -1152,10 +1163,10 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>865</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>678</v>
       </c>
     </row>
@@ -1165,10 +1176,10 @@
           <t>Calls while staffed</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="14" t="n">
         <v>421</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>341</v>
       </c>
     </row>
@@ -1178,10 +1189,10 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>275</v>
       </c>
     </row>
@@ -1191,26 +1202,26 @@
           <t>Answered while staffed</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <f>B20/B19</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="15">
         <f>C20/C19</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Calls outside staffed hours</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <f>(B18-B19)/B18</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>(C18-C19)/C18</f>
         <v/>
       </c>
@@ -1218,27 +1229,27 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Calls for help, March and February</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls while the line was staffed</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
@@ -1250,10 +1261,10 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="14" t="n">
         <v>865</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="14" t="n">
         <v>678</v>
       </c>
     </row>
@@ -1263,10 +1274,10 @@
           <t>Calls while staffed</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="14" t="n">
         <v>421</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="14" t="n">
         <v>341</v>
       </c>
     </row>
@@ -1276,10 +1287,10 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B30" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="14" t="n">
         <v>275</v>
       </c>
     </row>
@@ -1289,26 +1300,26 @@
           <t>Answered while staffed</t>
         </is>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="15">
         <f>B30/B29</f>
         <v/>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <f>C30/C29</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Calls outside staffed hours</t>
         </is>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <f>(B28-B29)/B28</f>
         <v/>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="17">
         <f>(C28-C29)/C28</f>
         <v/>
       </c>
@@ -1316,27 +1327,27 @@
     <row r="33"/>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Median wait when answered, March and February</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>The middle wait when every answered call is lined up from shortest to longest</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
@@ -1348,23 +1359,23 @@
           <t>Answered calls (while staffed)</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n">
+      <c r="B38" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="C38" s="13" t="n">
+      <c r="C38" s="14" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Median wait (seconds, rounded half up)</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B39" s="18" t="n">
         <v>77</v>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C39" s="18" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1378,22 +1389,22 @@
     <row r="41"/>
     <row r="42"/>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Calls before 8:30am, March 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1405,7 +1416,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
+      <c r="B46" s="14" t="n">
         <v>132</v>
       </c>
     </row>
@@ -1415,17 +1426,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n">
+      <c r="B47" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <f>B47/B46</f>
         <v/>
       </c>
@@ -1440,22 +1451,22 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Calls 8:30 to 10am, March 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1467,7 +1478,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n">
+      <c r="B55" s="14" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1477,17 +1488,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n">
+      <c r="B56" s="14" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="17">
         <f>B56/B55</f>
         <v/>
       </c>
@@ -1502,22 +1513,22 @@
     <row r="59"/>
     <row r="60"/>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Calls 10am to noon, March 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1529,7 +1540,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B64" s="13" t="n">
+      <c r="B64" s="14" t="n">
         <v>130</v>
       </c>
     </row>
@@ -1539,17 +1550,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
+      <c r="B65" s="14" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="17">
         <f>B65/B64</f>
         <v/>
       </c>
@@ -1564,22 +1575,22 @@
     <row r="68"/>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>Calls noon to 2pm, March 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr"/>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1591,7 +1602,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B73" s="13" t="n">
+      <c r="B73" s="14" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1601,17 +1612,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B74" s="13" t="n">
+      <c r="B74" s="14" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="17">
         <f>B74/B73</f>
         <v/>
       </c>
@@ -1626,22 +1637,22 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>Calls 2 to 5pm, March 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr"/>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1653,7 +1664,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B82" s="13" t="n">
+      <c r="B82" s="14" t="n">
         <v>152</v>
       </c>
     </row>
@@ -1663,17 +1674,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B83" s="13" t="n">
+      <c r="B83" s="14" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="inlineStr">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="17">
         <f>B83/B82</f>
         <v/>
       </c>
@@ -1688,22 +1699,22 @@
     <row r="86"/>
     <row r="87"/>
     <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>Calls 5 to 8pm, March 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr"/>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1715,7 +1726,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B91" s="13" t="n">
+      <c r="B91" s="14" t="n">
         <v>181</v>
       </c>
     </row>
@@ -1725,17 +1736,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B92" s="13" t="n">
+      <c r="B92" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="inlineStr">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="17">
         <f>B92/B91</f>
         <v/>
       </c>
@@ -1750,22 +1761,22 @@
     <row r="95"/>
     <row r="96"/>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>Calls after 8pm, March 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>Answered ÷ calls</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr"/>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
@@ -1777,7 +1788,7 @@
           <t>Calls</t>
         </is>
       </c>
-      <c r="B100" s="13" t="n">
+      <c r="B100" s="14" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1787,17 +1798,17 @@
           <t>Answered</t>
         </is>
       </c>
-      <c r="B101" s="13" t="n">
+      <c r="B101" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="B102" s="16">
+      <c r="B102" s="17">
         <f>B101/B100</f>
         <v/>
       </c>
@@ -1818,7 +1829,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1866,489 +1877,489 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: March 2026 · Data status: Feb 2026 locked · Mar 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Calls</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>While staffed</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Answered while staffed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>685</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>329</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>299</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <f>IF(D6=0,"",E6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>633</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>307</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>278</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <f>IF(D7=0,"",E7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>684</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>284</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <f>IF(D8=0,"",E8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>690</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>324</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>280</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <f>IF(D9=0,"",E9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>664</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>320</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>278</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <f>IF(D10=0,"",E10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>685</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>311</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>284</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="15">
         <f>IF(D11=0,"",E11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>629</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>286</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>246</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="15">
         <f>IF(D12=0,"",E12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>724</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>348</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>302</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="15">
         <f>IF(D13=0,"",E13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>820</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>389</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>330</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="15">
         <f>IF(D14=0,"",E14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>909</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>477</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>402</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="15">
         <f>IF(D15=0,"",E15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>826</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>388</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>327</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="15">
         <f>IF(D16=0,"",E16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>756</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>359</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>307</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <f>IF(D17=0,"",E17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>770</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>363</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>304</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="15">
         <f>IF(D18=0,"",E18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>746</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>357</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>297</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="15">
         <f>IF(D19=0,"",E19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>776</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>357</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>282</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="15">
         <f>IF(D20=0,"",E20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>726</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>346</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>297</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="15">
         <f>IF(D21=0,"",E21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>678</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>341</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>275</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="15">
         <f>IF(D22=0,"",E22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>865</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>421</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>338</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="15">
         <f>IF(D23=0,"",E23/D23)</f>
         <v/>
       </c>
@@ -2359,7 +2370,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 calls.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
